--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -78,12 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
+        <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,13 +130,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 01 Jun 2026 16:24 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 01 Jul 2026 13:20 IST</t>
         </is>
       </c>
     </row>
@@ -583,154 +583,146 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>26550</v>
+        <v>1494.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>25150</v>
+        <v>1319.4</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>26855</v>
+        <v>1520.8</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>25175</v>
+        <v>1247.6</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>ABCAPITAL</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>354.65</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>287.7</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>363.3</v>
-      </c>
-      <c r="G4" s="8" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>375.95</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>339.45</v>
       </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>391.95</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>334.8</v>
+      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2710</v>
+        <v>594.85</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2073</v>
+        <v>500.81</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3132.5</v>
+        <v>667.9</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2538</v>
+        <v>542</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1463.65</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>903.15</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>1513.3</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>1236.6</v>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>ABSLAMC</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1123.5</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>979.1</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1005.6</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -739,76 +731,76 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2443.8</v>
+        <v>966.75</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1770.1</v>
+        <v>845.55</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2937.4</v>
+        <v>1024</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2375</v>
+        <v>850.5</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>1271.95</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>814.75</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>1475.4</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>1227.15</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>267.65</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>295.9</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -817,76 +809,76 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1677</v>
+        <v>3184.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1332.6</v>
+        <v>2538</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1804.6</v>
+        <v>3526.2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1657.3</v>
+        <v>2902</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>226.24</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>150.62</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>243.37</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>208.03</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>3026.15</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2373.94</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>3036</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>2865.2</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -895,154 +887,150 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4110</v>
+        <v>774</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3555.2</v>
+        <v>646.05</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4503.6</v>
+        <v>1173.95</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3700</v>
+        <v>747.55</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ANGELONE</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>330.23</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>228.45</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>337.3</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>290.8</v>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>AEGISVOPAK</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>221</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>188.38</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>234.69</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>182.5</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12850</v>
+        <v>4551.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9298.5</v>
+        <v>3700</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>13118</v>
+        <v>5081.4</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>11864</v>
+        <v>4290.5</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>7878.5</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>7150.5</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>8176.5</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>7636.5</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3314.9</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2822.7</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>3422.7</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>2851.5</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1051,76 +1039,72 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>887.2</v>
+        <v>1849.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>790.75</v>
+        <v>1715.35</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>902.6</v>
+        <v>1976.7</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>793.95</v>
+        <v>1710.6</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>ASIANPAINT</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>2582</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>2142.4</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>2671.6</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>2415</v>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>13580</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>11864</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>15695</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>12511</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1129,76 +1113,76 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>721.34</v>
+        <v>8443</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>649.16</v>
+        <v>7636.5</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>728.35</v>
+        <v>8682</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>701.05</v>
+        <v>7816</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>684.9</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>509.15</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>773.3</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>588.1</v>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>428.75</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>378.05</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1207,76 +1191,76 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9905.6</v>
+        <v>776.55</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>8504.32</v>
+        <v>701.05</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10314.84</v>
+        <v>784.45</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>9855.299999999999</v>
+        <v>711.3</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>204.44</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>140.7</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>208.3</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>186.55</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1003.9</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>873.6</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1140.55</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>927.6</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1285,76 +1269,76 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>490</v>
+        <v>1550</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>405.75</v>
+        <v>1367</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>500.6</v>
+        <v>1578.7</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>465.9</v>
+        <v>1391</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>1949.9</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>1610.2</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>1957.2</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>1818.3</v>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>1317</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>1222.1</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1345.7</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>1230.3</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1363,76 +1347,72 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>358.1</v>
+        <v>986.1900000000001</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>239.17</v>
+        <v>883.5700000000001</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>416.75</v>
+        <v>1004.75</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>352.41</v>
+        <v>860.45</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>371.9</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>337.7</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>428.65</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>359.2</v>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>265.66</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>247.3</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>258</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1441,76 +1421,76 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3675.5</v>
+        <v>228.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2763</v>
+        <v>202.51</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4146.1</v>
+        <v>238.57</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3640.5</v>
+        <v>210.51</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>778.05</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>630.45</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>791.5</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>715.5</v>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>2044</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1818.3</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2144.1</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1870.5</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1519,76 +1499,76 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1799.8</v>
+        <v>521.55</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1508</v>
+        <v>408.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2024.5</v>
+        <v>525.2</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1710.5</v>
+        <v>434.8</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>CARBORUNIV</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>981.95</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>788.95</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>1029.05</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>951.75</v>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>38855</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>34825</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>39900</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>35755</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1597,76 +1577,76 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>815.25</v>
+        <v>2099</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>510.3</v>
+        <v>1710.5</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1071.15</v>
+        <v>2626</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>815.25</v>
+        <v>1950</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>CGCL</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>191.56</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>162.86</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>198.36</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>180.73</v>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>CARBORUNIV</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1166.4</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>951.75</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1178.2</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>993.2</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1675,76 +1655,76 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>846.9</v>
+        <v>2115</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>655.6</v>
+        <v>1606</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>917.45</v>
+        <v>2693</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>794.1</v>
+        <v>1720.1</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>CIPLA</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>1329.8</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>1165.7</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>1401</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>1274.7</v>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1152.7</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1305.5</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>1183</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1753,76 +1733,72 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CEATLTD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1334.9</v>
+        <v>3477</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1130</v>
+        <v>3093.6</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1421.8</v>
+        <v>3482.6</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1147.1</v>
+        <v>3061.2</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>CPPLUS</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>2389.9</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>1762</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>2903.5</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>2223.9</v>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>1087.12</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>813.17</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1298.7</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>1003.1</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1831,76 +1807,76 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>7933</v>
+        <v>204.9</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6665</v>
+        <v>180.73</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9074</v>
+        <v>227.66</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>7612.5</v>
+        <v>195.09</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>280.89</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>224.85</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>281.15</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>270.3</v>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>944.1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>794.1</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>952.15</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>883.05</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1909,76 +1885,72 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>5324.8</v>
+        <v>810</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>4470</v>
+        <v>736</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5881</v>
+        <v>814.9</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>5147.5</v>
+        <v>720.35</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>DEEPAKFERT</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>1292.5</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>933.6</v>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>1410.1</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>1211</v>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>973.1</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1156.3</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1060.2</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1987,154 +1959,146 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>6549.5</v>
+        <v>702</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>5647.5</v>
+        <v>651.55</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6667</v>
+        <v>753.2</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>6483.5</v>
+        <v>632.05</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>EMMVEE</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>299.5</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>210.05</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>247.05</v>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1734.8</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1491</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1789.8</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1444.6</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I40" s="6" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2477</v>
+        <v>1431.07</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2142.8</v>
+        <v>1262.85</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2722.6</v>
+        <v>1465.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2321.5</v>
+        <v>1341.1</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>ENRIN</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>3368</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>2521.7</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>3872.1</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>3013.6</v>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>1449.8</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1147.1</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1465.7</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>1356.2</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2143,76 +2107,72 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>370.3</v>
+        <v>1234.2</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>289.7</v>
+        <v>1040.3</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>386.5</v>
+        <v>1280.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>333.5</v>
+        <v>1022.2</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>FINCABLES</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>1022</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>765.5</v>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>1136.3</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>967.55</v>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>2903.5</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>2223.9</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>3647</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>3047.5</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2221,76 +2181,76 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3624</v>
+        <v>4303</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3033</v>
+        <v>3565.6</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3629</v>
+        <v>4501.8</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>3550</v>
+        <v>3801</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>FSL</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>254.68</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>205.82</v>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>262.73</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>213.21</v>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>DEEPAKFERT</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>1503.4</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1558.1</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>1376.3</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2299,76 +2259,76 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1048.7</v>
+        <v>620</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>835.8</v>
+        <v>553.8</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1100.1</v>
+        <v>620.05</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1012.5</v>
+        <v>555.5</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>1832</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>1652</v>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>1748</v>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1346.8</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1357.1</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>1248.4</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2377,76 +2337,76 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>100</v>
+        <v>1830</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>1627.4</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>100.37</v>
+        <v>1836</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>92.3</v>
+        <v>1667</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>GODREJIND</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>1043.4</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>756</v>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>1107.3</v>
-      </c>
-      <c r="G50" s="8" t="n">
-        <v>949.05</v>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>329.95</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>247.05</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>343</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>300.6</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2455,76 +2415,76 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>730.8</v>
+        <v>260.52</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>602.2</v>
+        <v>233.61</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>773.85</v>
+        <v>264.6</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>690.05</v>
+        <v>234.25</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>2848.2</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>2514.2</v>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>3122.4</v>
-      </c>
-      <c r="G52" s="8" t="n">
-        <v>2794.5</v>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>298.45</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>277.1</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>284.85</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2533,154 +2493,146 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>4694</v>
+        <v>502.15</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>3650</v>
+        <v>413.55</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>5148.6</v>
+        <v>505.1</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>4231.1</v>
+        <v>415.35</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>HEXT</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>496.62</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>414.86</v>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>498.58</v>
-      </c>
-      <c r="G54" s="8" t="n">
-        <v>439.35</v>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>FLUOROCHEM</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>3878</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>3550</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>3964</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>3451.2</v>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I54" s="6" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>119.5</v>
+        <v>1154</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>1012.5</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>179.94</v>
+        <v>1239.3</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>116.03</v>
+        <v>975.6</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I55" s="3" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>1080</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>884.8</v>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>1126.7</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>1022.1</v>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>170.7</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>151.41</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>173.46</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>161.18</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2689,76 +2641,76 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>388</v>
+        <v>2396</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>317.75</v>
+        <v>1748</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>393.85</v>
+        <v>2495</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>355.8</v>
+        <v>2167.8</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>621.9400000000001</v>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>494.32</v>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="n">
-        <v>632.95</v>
-      </c>
-      <c r="G58" s="8" t="n">
-        <v>595.95</v>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>104.14</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>112.09</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>95.47</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2767,76 +2719,72 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>GODIGIT</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>359.75</v>
+        <v>320.9</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>295</v>
+        <v>300.35</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>406.4</v>
+        <v>322.75</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>331</v>
+        <v>290.8</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I59" s="3" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>HONAUT</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>33100</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>26545</v>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="n">
-        <v>35520</v>
-      </c>
-      <c r="G60" s="8" t="n">
-        <v>28000</v>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>804.3</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>690.05</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>813.25</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>736.5</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2845,76 +2793,72 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1921.7</v>
+        <v>702.99</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1658</v>
+        <v>652.1900000000001</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1924</v>
+        <v>750.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1760</v>
+        <v>613.2</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I61" s="3" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>10.22</v>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>788.51</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>725.75</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>797.95</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>732.3</v>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2923,76 +2867,76 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>71.15000000000001</v>
+        <v>189.08</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>58.08</v>
+        <v>116.03</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>71.31999999999999</v>
+        <v>212.85</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>66.16</v>
+        <v>160.66</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>IFCI</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>49.88</v>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="n">
-        <v>68.53</v>
-      </c>
-      <c r="G64" s="8" t="n">
-        <v>57.87</v>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>424.9</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>331</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>457.9</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>396.1</v>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3001,76 +2945,76 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1669</v>
+        <v>36550</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1302.5</v>
+        <v>28000</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1675.6</v>
+        <v>39735</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>1519.5</v>
+        <v>34240</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>INDGN</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>508.45</v>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>442.35</v>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="n">
-        <v>521.55</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>499.75</v>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>654.45</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>539.6</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>679.2</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>580.9</v>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3079,76 +3023,72 @@
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>135.68</v>
+        <v>1301.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>109.78</v>
+        <v>1223.3</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>140.36</v>
+        <v>1375.2</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>126.12</v>
+        <v>1213.7</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I67" s="3" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>JBCHEPHARM</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>2103</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>1892.6</v>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>2167.4</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>2043.4</v>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>IDBI</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>83.53</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>71.48</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3157,76 +3097,76 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>21.05</v>
+        <v>14.44</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>14.34</v>
+        <v>10.22</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>21.87</v>
+        <v>14.46</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>17.1</v>
+        <v>13.73</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>JSWDULUX</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="n">
-        <v>3064.2</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>2758</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>3151.8</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>2857</v>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>69.53</v>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3235,76 +3175,76 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>585.65</v>
+        <v>70.2</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>466.3</v>
+        <v>57.87</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>595.05</v>
+        <v>74.88</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>505.2</v>
+        <v>66.61</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>JUBLPHARMA</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>959.35</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>800.05</v>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>995</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>927.25</v>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>507.8</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>459.7</v>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3313,76 +3253,76 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>5050</v>
+        <v>675.49</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3953.3</v>
+        <v>619.6900000000001</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>5267.5</v>
+        <v>713.95</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>4720.1</v>
+        <v>635</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>KIMS</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>691.9</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>613</v>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="n">
-        <v>758.85</v>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>663</v>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>4593.2</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>4146.3</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>5368.4</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>4350</v>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3391,154 +3331,146 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1745.9</v>
+        <v>1678.3</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1320.3</v>
+        <v>1482.9</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1928</v>
+        <v>1701</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1536.1</v>
+        <v>1470</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I75" s="3" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>KPIL</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="n">
-        <v>1275</v>
-      </c>
-      <c r="D76" s="8" t="n">
-        <v>1049</v>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="n">
-        <v>1305</v>
-      </c>
-      <c r="G76" s="8" t="n">
-        <v>1210.1</v>
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>ITCHOTELS</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>170.25</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>150.55</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>179.99</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>148.45</v>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I76" s="6" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>767.2</v>
+        <v>145</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>648.8</v>
+        <v>126.12</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>771.95</v>
+        <v>154.74</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>690.45</v>
+        <v>138.91</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>KPRMILL</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="n">
-        <v>946.5</v>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>814.05</v>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>966.5</v>
-      </c>
-      <c r="G78" s="8" t="n">
-        <v>883.15</v>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>2285.3</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>2043.4</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>2295.9</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>2080.9</v>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3547,76 +3479,76 @@
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1471.5</v>
+        <v>251.7</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1285</v>
+        <v>214.01</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1607.4</v>
+        <v>261.49</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>1367.2</v>
+        <v>221.7</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="n">
-        <v>1143.71</v>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>993.26</v>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>1360.65</v>
-      </c>
-      <c r="G80" s="8" t="n">
-        <v>1099.85</v>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>3170.6</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>2857</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>3228.1</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>3056.3</v>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3625,76 +3557,76 @@
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1785.2</v>
+        <v>294.91</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>1290</v>
+        <v>255.23</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1802.1</v>
+        <v>322.15</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>1636.1</v>
+        <v>266.55</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>LODHA</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="n">
-        <v>921.45</v>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>650.8</v>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="n">
-        <v>938.1</v>
-      </c>
-      <c r="G82" s="8" t="n">
-        <v>830.2</v>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>1187.65</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1041.2</v>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>1210.4</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>1060.1</v>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3703,76 +3635,76 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>301.97</v>
+        <v>791.15</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>247.41</v>
+        <v>663</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>324.89</v>
+        <v>814.6</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>291.59</v>
+        <v>725.4</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n">
-        <v>2322.2</v>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>1928</v>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>2375.6</v>
-      </c>
-      <c r="G84" s="8" t="n">
-        <v>2239.6</v>
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>1943.7</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1536.1</v>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>2364</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>1791.1</v>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3781,76 +3713,76 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>794</v>
+        <v>1329</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>728.95</v>
+        <v>1210.1</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>821.7</v>
+        <v>1370.1</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>760.6</v>
+        <v>1240.1</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>MEDANTA</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="n">
-        <v>1179</v>
-      </c>
-      <c r="D86" s="8" t="n">
-        <v>959.65</v>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>1189</v>
-      </c>
-      <c r="G86" s="8" t="n">
-        <v>1112.1</v>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>989.15</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>883.15</v>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>1177.3</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>965.55</v>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3859,76 +3791,76 @@
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>551.75</v>
+        <v>1393.4</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>490</v>
+        <v>1100.95</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>624.4</v>
+        <v>1517.4</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>502</v>
+        <v>1342.9</v>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="n">
-        <v>132.99</v>
-      </c>
-      <c r="D88" s="8" t="n">
-        <v>102.82</v>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="n">
-        <v>145.74</v>
-      </c>
-      <c r="G88" s="8" t="n">
-        <v>118.41</v>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>418.73</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>431.65</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>391.55</v>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3937,232 +3869,220 @@
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>835.5</v>
+        <v>4139.5</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>655.65</v>
+        <v>3847</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>879.5</v>
+        <v>4143.4</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>800.25</v>
+        <v>3854.4</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>NAM-INDIA</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="n">
-        <v>1065</v>
-      </c>
-      <c r="D90" s="8" t="n">
-        <v>810</v>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="n">
-        <v>1100.2</v>
-      </c>
-      <c r="G90" s="8" t="n">
-        <v>1005.2</v>
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>262.75</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>310.75</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>256.1</v>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I90" s="6" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>96.5</v>
+        <v>84.61</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>79.29000000000001</v>
+        <v>75.06</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>100.26</v>
+        <v>91.44</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>89.83</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="n">
-        <v>4174.8</v>
-      </c>
-      <c r="D92" s="8" t="n">
-        <v>3043.3</v>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="n">
-        <v>4670.7</v>
-      </c>
-      <c r="G92" s="8" t="n">
-        <v>3671.1</v>
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>13976</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>12753</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>14115</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>12700</v>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I92" s="6" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>15491</v>
+        <v>1111</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>12060</v>
+        <v>955</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>17088</v>
+        <v>1129.25</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>15003</v>
+        <v>919.8</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I93" s="3" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="n">
-        <v>1838</v>
-      </c>
-      <c r="D94" s="8" t="n">
-        <v>1589</v>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="n">
-        <v>1894</v>
-      </c>
-      <c r="G94" s="8" t="n">
-        <v>1741.2</v>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>MEDANTA</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>1278</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>1112.1</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>1313.8</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>1153</v>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4171,76 +4091,76 @@
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>NIVABUPA</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>81.81</v>
+        <v>635</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>70</v>
+        <v>502</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>83.5</v>
+        <v>696.8</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>77.68000000000001</v>
+        <v>610.8</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="n">
-        <v>328.7</v>
-      </c>
-      <c r="D96" s="8" t="n">
-        <v>261.1</v>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="n">
-        <v>347.55</v>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>306.3</v>
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>909</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>800.25</v>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="n">
+        <v>951.3</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>812.25</v>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4249,76 +4169,76 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>NSLNISP</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>43.54</v>
+        <v>1112.85</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>34.07</v>
+        <v>994.34</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>44.62</v>
+        <v>1162</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>41.75</v>
+        <v>1037.9</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="n">
-        <v>1401.6</v>
-      </c>
-      <c r="D98" s="8" t="n">
-        <v>1098.99</v>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="n">
-        <v>1539.87</v>
-      </c>
-      <c r="G98" s="8" t="n">
-        <v>1303.53</v>
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>7515.96</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>6747.38</v>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>7687</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>6786</v>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4327,76 +4247,76 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>318</v>
+        <v>102.67</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>279.9</v>
+        <v>89.83</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>348.65</v>
+        <v>104.93</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>288.45</v>
+        <v>99.06</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="n">
-        <v>9551.370000000001</v>
-      </c>
-      <c r="D100" s="8" t="n">
-        <v>6518.26</v>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="n">
-        <v>9686.49</v>
-      </c>
-      <c r="G100" s="8" t="n">
-        <v>8405.690000000001</v>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>NEULANDLAB</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>18305</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>15003</v>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>18579</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>16401</v>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4405,232 +4325,224 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1424.8</v>
+        <v>1968</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1259</v>
+        <v>1741.2</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1482.8</v>
+        <v>1971.7</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1347.7</v>
+        <v>1833.6</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I101" s="6" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>POLYCAB</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="n">
-        <v>8338.5</v>
-      </c>
-      <c r="D102" s="8" t="n">
-        <v>6690.5</v>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="n">
-        <v>9477.5</v>
-      </c>
-      <c r="G102" s="8" t="n">
-        <v>8062.5</v>
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>178.01</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>145.5</v>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I102" s="6" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>33795</v>
+        <v>1647.9</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>24180</v>
+        <v>1316</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>38445</v>
+        <v>1806.4</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>31195</v>
+        <v>1497.6</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I103" s="6" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="n">
-        <v>171.65</v>
-      </c>
-      <c r="D104" s="8" t="n">
-        <v>136.26</v>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="n">
-        <v>172.79</v>
-      </c>
-      <c r="G104" s="8" t="n">
-        <v>157.77</v>
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>310.85</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>257.8</v>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I104" s="6" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1050.03</v>
+        <v>1744</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>883.4</v>
+        <v>1571</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1060.22</v>
+        <v>1769.2</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>942.41</v>
+        <v>1575.1</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="n">
-        <v>3475</v>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>2587.2</v>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="n">
-        <v>3518.6</v>
-      </c>
-      <c r="G106" s="8" t="n">
-        <v>3302</v>
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>10584.5</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>8646.5</v>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>10775.5</v>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>9050</v>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4639,76 +4551,76 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1322</v>
+        <v>42.88</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>1120.5</v>
+        <v>33.55</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1380.3</v>
+        <v>43.76</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>1236.5</v>
+        <v>38.08</v>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="n">
-        <v>1648</v>
-      </c>
-      <c r="D108" s="8" t="n">
-        <v>1281.3</v>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="n">
-        <v>2056.3</v>
-      </c>
-      <c r="G108" s="8" t="n">
-        <v>1571</v>
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>OLECTRA</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>1397.9</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>1166.4</v>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>1499.6</v>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>1219.4</v>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4717,76 +4629,76 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>189.1</v>
+        <v>40490</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>150.28</v>
+        <v>34720</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>204.37</v>
+        <v>41370</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>175.16</v>
+        <v>36585</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>SAILIFE</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="n">
-        <v>1089.9</v>
-      </c>
-      <c r="D110" s="8" t="n">
-        <v>927.05</v>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="n">
-        <v>1160</v>
-      </c>
-      <c r="G110" s="8" t="n">
-        <v>949.3</v>
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>PARADEEP</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>115.35</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>136.03</v>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>120.49</v>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I110" s="6" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4795,150 +4707,150 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>157.8</v>
+        <v>313</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>138.75</v>
+        <v>262.85</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>177.01</v>
+        <v>321.15</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>134.75</v>
+        <v>275.7</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="n">
-        <v>365</v>
-      </c>
-      <c r="D112" s="8" t="n">
-        <v>308.8</v>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="n">
-        <v>424.15</v>
-      </c>
-      <c r="G112" s="8" t="n">
-        <v>328.1</v>
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>1855.9</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>1948.6</v>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>1675</v>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I112" s="6" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1249.8</v>
+        <v>1515</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>841.5</v>
+        <v>1347.7</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1308.8</v>
+        <v>1592.7</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1175</v>
+        <v>1430</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I113" s="6" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>SHYAMMETL</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="n">
-        <v>908.6</v>
-      </c>
-      <c r="D114" s="8" t="n">
-        <v>766.6</v>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="n">
-        <v>973.35</v>
-      </c>
-      <c r="G114" s="8" t="n">
-        <v>829.35</v>
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>2019.54</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>1851.6</v>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>2164.1</v>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>1886</v>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I114" s="6" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4947,76 +4859,76 @@
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>15995</v>
+        <v>9700.969999999999</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>12233</v>
+        <v>8024.43</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>18247</v>
+        <v>9961</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>15351</v>
+        <v>9320.5</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I115" s="6" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>SRF</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="n">
-        <v>2604</v>
-      </c>
-      <c r="D116" s="8" t="n">
-        <v>2355</v>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="n">
-        <v>2715.8</v>
-      </c>
-      <c r="G116" s="8" t="n">
-        <v>2495</v>
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>1514.7</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>1297.9</v>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>1564.6</v>
+      </c>
+      <c r="G116" s="7" t="n">
+        <v>1311</v>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5025,76 +4937,72 @@
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>453.8</v>
+        <v>118.9</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>368.85</v>
+        <v>102.63</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>501.55</v>
+        <v>124.13</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>419.15</v>
+        <v>89.8</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I117" s="3" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>SYRMA</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="n">
-        <v>1032</v>
-      </c>
-      <c r="D118" s="8" t="n">
-        <v>765.2</v>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="n">
-        <v>1088.55</v>
-      </c>
-      <c r="G118" s="8" t="n">
-        <v>957.4</v>
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>3679</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>3302</v>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>3945.5</v>
+      </c>
+      <c r="G118" s="7" t="n">
+        <v>3426.5</v>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I118" s="6" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5103,76 +5011,76 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1623</v>
+        <v>1394</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>1322.5</v>
+        <v>1236.5</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1965</v>
+        <v>1414.2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>1530.4</v>
+        <v>1311</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="n">
-        <v>605</v>
-      </c>
-      <c r="D120" s="8" t="n">
-        <v>517</v>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="n">
-        <v>705.3</v>
-      </c>
-      <c r="G120" s="8" t="n">
-        <v>578.25</v>
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>353</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>369.05</v>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>333</v>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5181,76 +5089,76 @@
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>461.5</v>
+        <v>228.3</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>396.25</v>
+        <v>208.1</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>520.4</v>
+        <v>276.18</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>414.5</v>
+        <v>225</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I121" s="6" t="inlineStr">
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="n">
-        <v>4305</v>
-      </c>
-      <c r="D122" s="8" t="n">
-        <v>3192.7</v>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="n">
-        <v>4982.7</v>
-      </c>
-      <c r="G122" s="8" t="n">
-        <v>4056.7</v>
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>2111.68</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>1567.05</v>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>2395.2</v>
+      </c>
+      <c r="G122" s="7" t="n">
+        <v>1964.3</v>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I122" s="6" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5259,76 +5167,76 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>805</v>
+        <v>1184.8</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>584.6</v>
+        <v>949.3</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>826.15</v>
+        <v>1234.3</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>721.2</v>
+        <v>1109.2</v>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>TMPV</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="n">
-        <v>367.95</v>
-      </c>
-      <c r="D124" s="8" t="n">
-        <v>295.05</v>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F124" s="8" t="n">
-        <v>393.9</v>
-      </c>
-      <c r="G124" s="8" t="n">
-        <v>333.65</v>
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>443</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="G124" s="7" t="n">
+        <v>433.25</v>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5337,76 +5245,72 @@
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>4333</v>
+        <v>1023.75</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>3871.1</v>
+        <v>901.3</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>4410.8</v>
+        <v>1042.15</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>4185.1</v>
+        <v>879.1</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I125" s="3" t="inlineStr"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="n">
-        <v>605.95</v>
-      </c>
-      <c r="D126" s="8" t="n">
-        <v>440.8</v>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="n">
-        <v>741.5</v>
-      </c>
-      <c r="G126" s="8" t="n">
-        <v>543.5</v>
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>STARHEALTH</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>535.95</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>491.9</v>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>588.95</v>
+      </c>
+      <c r="G126" s="7" t="n">
+        <v>513</v>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5415,76 +5319,76 @@
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>472</v>
+        <v>58.42</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>390</v>
+        <v>51.31</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>506.05</v>
+        <v>58.9</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>446.75</v>
+        <v>52.56</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
+      <c r="I127" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>VIJAYA</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="n">
-        <v>1135</v>
-      </c>
-      <c r="D128" s="8" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="n">
-        <v>1308.5</v>
-      </c>
-      <c r="G128" s="8" t="n">
-        <v>1129.6</v>
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>957.4</v>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>1396.3</v>
+      </c>
+      <c r="G128" s="7" t="n">
+        <v>1085.9</v>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I128" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5493,154 +5397,150 @@
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>TARIL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>1290</v>
+        <v>338</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>805.45</v>
+        <v>287.5</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1376.9</v>
+        <v>351.35</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1231.1</v>
+        <v>299.7</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr">
+      <c r="I129" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>WELSPUNLIV</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="n">
-        <v>136.45</v>
-      </c>
-      <c r="D130" s="8" t="n">
-        <v>110.8</v>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F130" s="8" t="n">
-        <v>137.97</v>
-      </c>
-      <c r="G130" s="8" t="n">
-        <v>127.3</v>
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>296</v>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1532</v>
+        <v>1310.3</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>1198.4</v>
+        <v>1126.4</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>2031.4</v>
+        <v>1429.7</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1395.6</v>
+        <v>1163.5</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I131" s="6" t="inlineStr">
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>YESBANK</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="D132" s="8" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="G132" s="8" t="n">
-        <v>19.76</v>
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>TEJASNET</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>554.95</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="n">
+        <v>612.5</v>
+      </c>
+      <c r="G132" s="7" t="n">
+        <v>518.2</v>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I132" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5649,61 +5549,560 @@
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>962.9</v>
+        <v>433.45</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>835.5</v>
+        <v>402.55</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1077.7</v>
+        <v>475.45</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>891.9</v>
+        <v>400.1</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Total Breakout Stocks: 131</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>Full Breakout (Close &gt; Prev High  AND  Low &gt; Prev Low): 130</t>
+      <c r="I133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>5075</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>4056.7</v>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="n">
+        <v>5159.5</v>
+      </c>
+      <c r="G134" s="7" t="n">
+        <v>4533.3</v>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>869.7</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>721.2</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>880.7</v>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>790</v>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>TRAVELFOOD</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>1318.8</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>1040</v>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="n">
+        <v>1323.4</v>
+      </c>
+      <c r="G136" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>2903.71</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>2649.82</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>3282.6</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>2680</v>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>171.79</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>156.21</v>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="n">
+        <v>172.43</v>
+      </c>
+      <c r="G138" s="7" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>1342.1</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>1350.4</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>1229.2</v>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>1390.18</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>1227.03</v>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="n">
+        <v>1521.9</v>
+      </c>
+      <c r="G140" s="7" t="n">
+        <v>1320</v>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>158.84</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>133.34</v>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="G142" s="7" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>ZEEL</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>103.51</v>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>ZENTEC</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>1721.7</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>1466.1</v>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="n">
+        <v>1773.4</v>
+      </c>
+      <c r="G144" s="7" t="n">
+        <v>1582.3</v>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>ZFCVINDIA</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>2558.17</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>2313.33</v>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>2566</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>2341.67</v>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>542</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>480</v>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>575.4</v>
+      </c>
+      <c r="G146" s="7" t="n">
+        <v>486.05</v>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>Total Breakout Stocks: 144</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>Full Breakout (Close &gt; Prev High  AND  Low &gt; Prev Low): 116</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A135:D135"/>
-    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="A148:D148"/>
+    <mergeCell ref="A149:D149"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -78,12 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
+        <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,13 +130,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 01 Jul 2026 13:20 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 01 Aug 2026 11:45 IST</t>
         </is>
       </c>
     </row>
@@ -583,146 +583,154 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1494.9</v>
+        <v>33805.42</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1319.4</v>
+        <v>30567.31</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1520.8</v>
+        <v>34615</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1247.6</v>
+        <v>33040</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>375.95</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>339.45</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>391.95</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>334.8</v>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>26553.64</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>24623.8</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>27800</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>25370</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>594.85</v>
+        <v>399.35</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>500.81</v>
+        <v>334.8</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>667.9</v>
+        <v>404.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>542</v>
+        <v>384</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>ABSLAMC</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1123.5</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>979.1</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>1154.7</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1005.6</v>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1364.92</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1152.99</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1418.1</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1323.6</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -736,71 +744,71 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>966.75</v>
+        <v>1047</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>845.55</v>
+        <v>850.5</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1024</v>
+        <v>1070.3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>850.5</v>
+        <v>957.8</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>ACMESOLAR</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>313.45</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>267.65</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>380.55</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>295.9</v>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1614.8</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1645.4</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>1470</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -809,76 +817,76 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3184.9</v>
+        <v>1189.61</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2538</v>
+        <v>743.59</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3526.2</v>
+        <v>1280.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2902</v>
+        <v>1163</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>3026.15</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>2373.94</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>3036</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>2865.2</v>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>AEGISVOPAK</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>249.25</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>182.37</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>290.16</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>230.41</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -887,150 +895,154 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>774</v>
+        <v>1535</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>646.05</v>
+        <v>1390.5</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1173.95</v>
+        <v>1586</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>747.55</v>
+        <v>1415.6</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>AEGISVOPAK</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>221</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>188.38</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>234.69</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>182.5</v>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>5608</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>5162.5</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>5751.5</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>5487</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4551.7</v>
+        <v>2032.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3700</v>
+        <v>1710.6</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5081.4</v>
+        <v>2073.7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4290.5</v>
+        <v>1945.1</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>AJANTPHARM</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>3314.9</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>2822.7</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>3422.7</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>2851.5</v>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ANANTRAJ</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>597.8200000000001</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>509.46</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>624.5</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>513</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1039,72 +1051,76 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1849.5</v>
+        <v>8770</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1715.35</v>
+        <v>7816</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1976.7</v>
+        <v>8957</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1710.6</v>
+        <v>8611.5</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>APARINDS</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>13580</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>11864</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>15695</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>12511</v>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>892.65</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>789.12</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>910.45</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>829.1</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1113,76 +1129,76 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>8443</v>
+        <v>162.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>7636.5</v>
+        <v>138.03</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8682</v>
+        <v>166.18</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>7816</v>
+        <v>147.59</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>APOLLOTYRE</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>428.75</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>365.3</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>378.05</v>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>1147.4</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>927.6</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>1260.3</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1116.2</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1191,76 +1207,76 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>776.55</v>
+        <v>10619</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>701.05</v>
+        <v>9501</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>784.45</v>
+        <v>11520.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>711.3</v>
+        <v>9716</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>1003.9</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>873.6</v>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>1140.55</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>927.6</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>1805.7</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1640.5</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>2029.1</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1741.5</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1269,76 +1285,76 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1550</v>
+        <v>10995</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1367</v>
+        <v>9816</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1578.7</v>
+        <v>11343</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1391</v>
+        <v>10132</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>1317</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>1222.1</v>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1345.7</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1230.3</v>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>1010.95</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>860.45</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>1141.2</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>993.4</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1347,72 +1363,76 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>986.1900000000001</v>
+        <v>2282.74</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>883.5700000000001</v>
+        <v>1966.33</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1004.75</v>
+        <v>2473.5</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>860.45</v>
+        <v>1982.1</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>265.66</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>247.3</v>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>272.4</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>258</v>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>570</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>541.55</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1421,76 +1441,76 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>228.8</v>
+        <v>1903.74</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>202.51</v>
+        <v>1746.62</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>238.57</v>
+        <v>1972</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>210.51</v>
+        <v>1845.6</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>2044</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>1818.3</v>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>2144.1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1870.5</v>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>BHARTIHEXA</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>1510.58</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>1414.44</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>1607.5</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>1437.1</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1499,76 +1519,76 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>BLUEDART</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>5079.5</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>4628.5</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>5160.3</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>4716.1</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
           <t>BLUEJET</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>521.55</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>408.9</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>525.2</v>
-      </c>
-      <c r="G27" s="4" t="n">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>547.6</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>434.8</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>38855</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>34825</v>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>39900</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>35755</v>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>626.25</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>513.1</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1577,76 +1597,76 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2099</v>
+        <v>5211.7</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1710.5</v>
+        <v>4952.52</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2626</v>
+        <v>5416.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1950</v>
+        <v>5115</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>CARBORUNIV</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>1166.4</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>951.75</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1178.2</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>993.2</v>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>CANHLIFE</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>138.11</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1655,76 +1675,76 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2115</v>
+        <v>1315.4</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1606</v>
+        <v>1003.1</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2693</v>
+        <v>1367.8</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1720.1</v>
+        <v>1274.6</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>CDSL</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>1291</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1152.7</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1305.5</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>1183</v>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>CGCL</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>231.36</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>195.09</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>232.38</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>218.59</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1733,72 +1753,76 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CEATLTD</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3477</v>
+        <v>1249</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3093.6</v>
+        <v>1060.2</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3482.6</v>
+        <v>1260.6</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3061.2</v>
+        <v>1080</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>CEMPRO</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>1087.12</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>813.17</v>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1298.7</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1003.1</v>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>CHOICEIN</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>760</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>632.05</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>822.95</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>751.7</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1807,76 +1831,76 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>204.9</v>
+        <v>1823.18</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>180.73</v>
+        <v>1444.03</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>227.66</v>
+        <v>1849.9</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>195.09</v>
+        <v>1660.4</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>944.1</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>794.1</v>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>952.15</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>883.05</v>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1550.44</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>1353.09</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>1721</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>1362.2</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1885,72 +1909,76 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>810</v>
+        <v>484.65</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>736</v>
+        <v>437.45</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>814.9</v>
+        <v>525.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>720.35</v>
+        <v>448.45</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>CHENNPETRO</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>1139</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>973.1</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1156.3</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>1060.2</v>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>CONCORDBIO</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>1399.52</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1016.12</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>1420.8</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>1238</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -1959,146 +1987,154 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>702</v>
+        <v>1496</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>651.55</v>
+        <v>1229.1</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>753.2</v>
+        <v>1592.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>632.05</v>
+        <v>1456.5</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>1734.8</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>1491</v>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1789.8</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>1444.6</v>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>4240.22</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>3766.32</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>4359.8</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>3855</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1431.07</v>
+        <v>1773.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1262.85</v>
+        <v>1605</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1465.4</v>
+        <v>1799.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1341.1</v>
+        <v>1683</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>1449.8</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>1147.1</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1465.7</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>1356.2</v>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>6859.21</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>6424.01</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>8056</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>6530.5</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2107,72 +2143,76 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1234.2</v>
+        <v>12930</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1040.3</v>
+        <v>11153</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1280.2</v>
+        <v>14049</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1022.2</v>
+        <v>11785</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>CPPLUS</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>2903.5</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>2223.9</v>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>3647</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>3047.5</v>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>636.01</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>548.61</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>659.3</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>618</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2181,76 +2221,76 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>4303</v>
+        <v>1551</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3565.6</v>
+        <v>1320</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4501.8</v>
+        <v>1845.5</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>3801</v>
+        <v>1328.2</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>DEEPAKFERT</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>1503.4</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>1211</v>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1558.1</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>1376.3</v>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>7673.64</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>6870.55</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>7833.5</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>7053.5</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2259,76 +2299,76 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>620</v>
+        <v>1944</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>553.8</v>
+        <v>1667</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>620.05</v>
+        <v>1960.1</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>555.5</v>
+        <v>1751</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>1346.8</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1230</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1357.1</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>1248.4</v>
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>2988.19</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>2669.79</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>3086</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>2880</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2337,76 +2377,76 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1830</v>
+        <v>267.5</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1627.4</v>
+        <v>234.25</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1836</v>
+        <v>302.45</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1667</v>
+        <v>265.3</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>EMMVEE</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>329.95</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>247.05</v>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>343</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>300.6</v>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>408.54</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>449.8</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>385.8</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2415,76 +2455,76 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>260.52</v>
+        <v>331.8</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>233.61</v>
+        <v>284.85</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>264.6</v>
+        <v>358.85</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>234.25</v>
+        <v>323</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>298.45</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>277.1</v>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>330.05</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>284.85</v>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>FIVESTAR</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>525.9400000000001</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>413.85</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>547.95</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>508</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2493,76 +2533,80 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>502.15</v>
+        <v>3990</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>413.55</v>
+        <v>3451.2</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>505.1</v>
+        <v>4366.8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>415.35</v>
+        <v>3814.2</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>FLUOROCHEM</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>3878</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>3550</v>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>3964</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>3451.2</v>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>302.12</v>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>228.7</v>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -2572,67 +2616,71 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1154</v>
+        <v>1285</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1012.5</v>
+        <v>975.6</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1239.3</v>
+        <v>1441.8</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>975.6</v>
+        <v>1215</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>170.7</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>151.41</v>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>173.46</v>
-      </c>
-      <c r="G56" s="7" t="n">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>178.47</v>
+      </c>
+      <c r="D56" s="8" t="n">
         <v>161.18</v>
       </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>181.44</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>167.27</v>
+      </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2641,76 +2689,76 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>2396</v>
+        <v>2460.9</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1748</v>
+        <v>2088.1</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2495</v>
+        <v>2655.4</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2167.8</v>
+        <v>2370</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>104.14</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>112.09</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>95.47</v>
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>1056.8</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>975.4</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1070.4</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>1013.9</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2719,72 +2767,76 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>GODIGIT</t>
+          <t>GODREJIND</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>320.9</v>
+        <v>1178.5</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>300.35</v>
+        <v>1005</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>322.75</v>
+        <v>1317.6</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>290.8</v>
+        <v>1164.4</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>804.3</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>690.05</v>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>813.25</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>736.5</v>
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>1878.52</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>1602.35</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>2105.7</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>1873.8</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2793,72 +2845,76 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>702.99</v>
+        <v>816</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>652.1900000000001</v>
+        <v>734.97</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>750.8</v>
+        <v>824.65</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>613.2</v>
+        <v>804.5</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>788.51</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>725.75</v>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>797.95</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>732.3</v>
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>4535</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>4148.8</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>4646.5</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>4305.8</v>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2867,154 +2923,150 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>189.08</v>
+        <v>1209.1</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>116.03</v>
+        <v>1123.6</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>212.85</v>
+        <v>1260.7</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>160.66</v>
+        <v>1141.2</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>HONASA</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>424.9</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>331</v>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>457.9</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>396.1</v>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>1244.3</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>1057.8</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>1346.9</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>1030</v>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I64" s="7" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>36550</v>
+        <v>567.89</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>28000</v>
+        <v>502.16</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>39735</v>
+        <v>657.25</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>34240</v>
+        <v>509.1</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>HSCL</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>654.45</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>539.6</v>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>679.2</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>580.9</v>
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>4999.86</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>4603.78</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>5386</v>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>4774</v>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3023,72 +3075,76 @@
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1301.8</v>
+        <v>552.5</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1223.3</v>
+        <v>472</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1375.2</v>
+        <v>561.65</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1213.7</v>
+        <v>512.5</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>IDBI</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>83.53</v>
-      </c>
-      <c r="G68" s="7" t="n">
-        <v>71.48</v>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>718</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>580.9</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>750.65</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>635.85</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3097,76 +3153,76 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>14.44</v>
+        <v>2059</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>10.22</v>
+        <v>1847.1</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>14.46</v>
+        <v>2180.7</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>13.73</v>
+        <v>1895.4</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>73.08</v>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>79.48999999999999</v>
-      </c>
-      <c r="G70" s="7" t="n">
-        <v>69.53</v>
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>1404</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>1213.7</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>1435.4</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>1367.7</v>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3175,154 +3231,150 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>70.2</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>57.87</v>
+        <v>69.53</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>74.88</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>66.61</v>
+        <v>77.47</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>IIFL</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>437.6</v>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>507.8</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>459.7</v>
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>129.22</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>132.24</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>116.26</v>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I72" s="7" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>675.49</v>
+        <v>546.15</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>619.6900000000001</v>
+        <v>459.7</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>713.95</v>
+        <v>608.65</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>635</v>
+        <v>494.65</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>INDIGO</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>4593.2</v>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>4146.3</v>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>5368.4</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>4350</v>
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>1619.2</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>1848.9</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>1670.1</v>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3331,146 +3383,154 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>953.5</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>881</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1012.45</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>927.05</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
           <t>IPCALAB</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>1678.3</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>1482.9</v>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>1701</v>
-      </c>
-      <c r="G75" s="4" t="n">
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>1736</v>
+      </c>
+      <c r="D76" s="8" t="n">
         <v>1470</v>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>ITCHOTELS</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="n">
-        <v>170.25</v>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>150.55</v>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="n">
-        <v>179.99</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>148.45</v>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>1747.8</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>1681.7</v>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>145</v>
+        <v>2317.5</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>126.12</v>
+        <v>2080.9</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>154.74</v>
+        <v>2416.1</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>138.91</v>
+        <v>2267.1</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>JBCHEPHARM</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="n">
-        <v>2285.3</v>
-      </c>
-      <c r="D78" s="7" t="n">
-        <v>2043.4</v>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>2295.9</v>
-      </c>
-      <c r="G78" s="7" t="n">
-        <v>2080.9</v>
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>246.85</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>256.46</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>229</v>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3479,154 +3539,150 @@
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>251.7</v>
+        <v>732.4</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>214.01</v>
+        <v>652.25</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>261.49</v>
+        <v>734.8</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>221.7</v>
+        <v>677.6</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>JSWDULUX</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="n">
-        <v>3170.6</v>
-      </c>
-      <c r="D80" s="7" t="n">
-        <v>2857</v>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>3228.1</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>3056.3</v>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>437.46</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>409.93</v>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>438.25</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>408.55</v>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I80" s="7" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>294.91</v>
+        <v>657.6900000000001</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>255.23</v>
+        <v>597.99</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>322.15</v>
+        <v>735.7</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>266.55</v>
+        <v>610.7</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="n">
-        <v>1187.65</v>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>1041.2</v>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="n">
-        <v>1210.4</v>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>1060.1</v>
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>JYOTICNC</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>791.1</v>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>580.1</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>808.65</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>745.75</v>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3635,76 +3691,76 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>KIMS</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>791.15</v>
+        <v>391.5</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>663</v>
+        <v>327.05</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>814.6</v>
+        <v>612.6</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>725.4</v>
+        <v>348.35</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>KIRLOSENG</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="n">
-        <v>1943.7</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>1536.1</v>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="n">
-        <v>2364</v>
-      </c>
-      <c r="G84" s="7" t="n">
-        <v>1791.1</v>
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>299.32</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>266.87</v>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>288.8</v>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3713,76 +3769,76 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>KPIL</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>1329</v>
+        <v>3399</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>1210.1</v>
+        <v>3018.1</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1370.1</v>
+        <v>3804.6</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>1240.1</v>
+        <v>3131</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>KPRMILL</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="n">
-        <v>989.15</v>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>883.15</v>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="n">
-        <v>1177.3</v>
-      </c>
-      <c r="G86" s="7" t="n">
-        <v>965.55</v>
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>915.6</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>789.36</v>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>937.9</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>838</v>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3791,76 +3847,76 @@
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>1798.21</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>1496.12</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1905.2</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>1610.1</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>1393.4</v>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>1100.95</v>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>1517.4</v>
-      </c>
-      <c r="G87" s="4" t="n">
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>1531.2</v>
+      </c>
+      <c r="D88" s="8" t="n">
         <v>1342.9</v>
       </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="n">
-        <v>418.73</v>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>379.14</v>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="n">
-        <v>431.65</v>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>391.55</v>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>1816.2</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>1448.2</v>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3869,298 +3925,306 @@
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>4139.5</v>
+        <v>532.5</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>3847</v>
+        <v>482.15</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>4143.4</v>
+        <v>561.4</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>3854.4</v>
+        <v>516.95</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="n">
-        <v>305.2</v>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>262.75</v>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="n">
-        <v>310.75</v>
-      </c>
-      <c r="G90" s="7" t="n">
-        <v>256.1</v>
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>1846.8</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>1670</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>2047</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>1708.9</v>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>84.61</v>
+        <v>972</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>75.06</v>
+        <v>848</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>91.44</v>
+        <v>1243.95</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>954.3</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="n">
-        <v>13976</v>
-      </c>
-      <c r="D92" s="7" t="n">
-        <v>12753</v>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="n">
-        <v>14115</v>
-      </c>
-      <c r="G92" s="7" t="n">
-        <v>12700</v>
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>364.05</v>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>410.35</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>367</v>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr"/>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1111</v>
+        <v>4360</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>955</v>
+        <v>3528</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1129.25</v>
+        <v>4362.1</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>919.8</v>
+        <v>3535.2</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>MEDANTA</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>1278</v>
-      </c>
-      <c r="D94" s="7" t="n">
-        <v>1112.1</v>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>1313.8</v>
-      </c>
-      <c r="G94" s="7" t="n">
-        <v>1153</v>
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>3090</v>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>3555.4</v>
+      </c>
+      <c r="G94" s="8" t="n">
+        <v>3030</v>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I94" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I94" s="7" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>635</v>
+        <v>3175.16</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>502</v>
+        <v>2870.26</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>696.8</v>
+        <v>3398.5</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>610.8</v>
+        <v>3079.4</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="n">
-        <v>909</v>
-      </c>
-      <c r="D96" s="7" t="n">
-        <v>800.25</v>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>951.3</v>
-      </c>
-      <c r="G96" s="7" t="n">
-        <v>812.25</v>
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="n">
+        <v>325.09</v>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>268.31</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>312</v>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4169,76 +4233,76 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1112.85</v>
+        <v>330.9</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>994.34</v>
+        <v>282.55</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1162</v>
+        <v>371.85</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>1037.9</v>
+        <v>315</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>NAVINFLUOR</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="n">
-        <v>7515.96</v>
-      </c>
-      <c r="D98" s="7" t="n">
-        <v>6747.38</v>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>7687</v>
-      </c>
-      <c r="G98" s="7" t="n">
-        <v>6786</v>
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>MAPMYINDIA</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="n">
+        <v>934.85</v>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>805</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>1181.65</v>
+      </c>
+      <c r="G98" s="8" t="n">
+        <v>813.5</v>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="I98" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4247,76 +4311,76 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>102.67</v>
+        <v>840.8099999999999</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>89.83</v>
+        <v>791.23</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>104.93</v>
+        <v>870.65</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>99.06</v>
+        <v>829.9</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="I99" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>NEULANDLAB</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>18305</v>
-      </c>
-      <c r="D100" s="7" t="n">
-        <v>15003</v>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>18579</v>
-      </c>
-      <c r="G100" s="7" t="n">
-        <v>16401</v>
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="n">
+        <v>14201</v>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>12700</v>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>14234</v>
+      </c>
+      <c r="G100" s="8" t="n">
+        <v>13197</v>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4325,224 +4389,232 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1968</v>
+        <v>1335.9</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1741.2</v>
+        <v>1153</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1971.7</v>
+        <v>1405.6</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1833.6</v>
+        <v>1295.9</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>NIACL</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>170.98</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>154</v>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>178.01</v>
-      </c>
-      <c r="G102" s="7" t="n">
-        <v>145.5</v>
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="n">
+        <v>132653.46</v>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>121837.34</v>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>132770</v>
+      </c>
+      <c r="G102" s="8" t="n">
+        <v>127480</v>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1647.9</v>
+        <v>1025.83</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>1316</v>
+        <v>946.13</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1806.4</v>
+        <v>1226.25</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1497.6</v>
+        <v>974.6</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="n">
-        <v>285.6</v>
-      </c>
-      <c r="D104" s="7" t="n">
-        <v>258.4</v>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>310.85</v>
-      </c>
-      <c r="G104" s="7" t="n">
-        <v>257.8</v>
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="n">
+        <v>1447.94</v>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>1361.55</v>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="n">
+        <v>1509.6</v>
+      </c>
+      <c r="G104" s="8" t="n">
+        <v>1405.1</v>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr"/>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1744</v>
+        <v>18740.36</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>1571</v>
+        <v>16370.74</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1769.2</v>
+        <v>19043</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1575.1</v>
+        <v>18055</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="n">
-        <v>10584.5</v>
-      </c>
-      <c r="D106" s="7" t="n">
-        <v>8646.5</v>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>10775.5</v>
-      </c>
-      <c r="G106" s="7" t="n">
-        <v>9050</v>
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>NEWGEN</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="n">
+        <v>532.04</v>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>430.18</v>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="n">
+        <v>555.7</v>
+      </c>
+      <c r="G106" s="8" t="n">
+        <v>461.25</v>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4551,76 +4623,76 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>42.88</v>
+        <v>1997.87</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>33.55</v>
+        <v>1829.54</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>43.76</v>
+        <v>2029.2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>38.08</v>
+        <v>1952</v>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>OLECTRA</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="n">
-        <v>1397.9</v>
-      </c>
-      <c r="D108" s="7" t="n">
-        <v>1166.4</v>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="n">
-        <v>1499.6</v>
-      </c>
-      <c r="G108" s="7" t="n">
-        <v>1219.4</v>
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="n">
+        <v>312.9</v>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>257.8</v>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="G108" s="8" t="n">
+        <v>305.6</v>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4629,76 +4701,76 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>40490</v>
+        <v>1782.97</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>34720</v>
+        <v>1573.4</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>41370</v>
+        <v>1827.7</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>36585</v>
+        <v>1758.5</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>PARADEEP</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="n">
-        <v>133.4</v>
-      </c>
-      <c r="D110" s="7" t="n">
-        <v>115.35</v>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="n">
-        <v>136.03</v>
-      </c>
-      <c r="G110" s="7" t="n">
-        <v>120.49</v>
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="n">
+        <v>11055</v>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>9050</v>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="n">
+        <v>11186</v>
+      </c>
+      <c r="G110" s="8" t="n">
+        <v>9937</v>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="I110" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4707,150 +4779,154 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>313</v>
+        <v>140.4</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>262.85</v>
+        <v>120.49</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>321.15</v>
+        <v>147.33</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>275.7</v>
+        <v>132.9</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I111" s="8" t="inlineStr">
+      <c r="I111" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="n">
-        <v>1855.9</v>
-      </c>
-      <c r="D112" s="7" t="n">
-        <v>1688</v>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>1948.6</v>
-      </c>
-      <c r="G112" s="7" t="n">
-        <v>1675</v>
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="n">
+        <v>1159.2</v>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G112" s="8" t="n">
+        <v>1150.5</v>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I112" s="6" t="inlineStr"/>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1515</v>
+        <v>4632.94</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>1347.7</v>
+        <v>4290.49</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1592.7</v>
+        <v>4823.9</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1430</v>
+        <v>4426</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="I113" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>PIRAMALFIN</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="n">
-        <v>2019.54</v>
-      </c>
-      <c r="D114" s="7" t="n">
-        <v>1851.6</v>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="n">
-        <v>2164.1</v>
-      </c>
-      <c r="G114" s="7" t="n">
-        <v>1886</v>
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="n">
+        <v>579</v>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>457</v>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="n">
+        <v>613.35</v>
+      </c>
+      <c r="G114" s="8" t="n">
+        <v>533.6</v>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="I114" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -4859,150 +4935,150 @@
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>9700.969999999999</v>
+        <v>1609.11</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>8024.43</v>
+        <v>1419.78</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>9961</v>
+        <v>1611.4</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>9320.5</v>
+        <v>1537.1</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>PRESTIGE</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="n">
-        <v>1514.7</v>
-      </c>
-      <c r="D116" s="7" t="n">
-        <v>1297.9</v>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="n">
-        <v>1564.6</v>
-      </c>
-      <c r="G116" s="7" t="n">
-        <v>1311</v>
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>102.67</v>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="G116" s="8" t="n">
+        <v>100.45</v>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I116" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I116" s="7" t="inlineStr"/>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>118.9</v>
+        <v>442.65</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>102.63</v>
+        <v>370.05</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>124.13</v>
+        <v>463.55</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>89.8</v>
+        <v>434.4</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr"/>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="n">
-        <v>3679</v>
-      </c>
-      <c r="D118" s="7" t="n">
-        <v>3302</v>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="n">
-        <v>3945.5</v>
-      </c>
-      <c r="G118" s="7" t="n">
-        <v>3426.5</v>
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="n">
+        <v>175.95</v>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="n">
+        <v>195.61</v>
+      </c>
+      <c r="G118" s="8" t="n">
+        <v>166.11</v>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I118" s="8" t="inlineStr">
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5011,76 +5087,76 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1394</v>
+        <v>1580.6</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>1236.5</v>
+        <v>1311</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1414.2</v>
+        <v>1616.2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>1311</v>
+        <v>1564.8</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="I119" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="n">
-        <v>353</v>
-      </c>
-      <c r="D120" s="7" t="n">
-        <v>318.45</v>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>369.05</v>
-      </c>
-      <c r="G120" s="7" t="n">
-        <v>333</v>
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="n">
+        <v>1003.45</v>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>934.2</v>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>1130.6</v>
+      </c>
+      <c r="G120" s="8" t="n">
+        <v>962</v>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="I120" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5089,76 +5165,76 @@
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>228.3</v>
+        <v>3966.4</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>208.1</v>
+        <v>3418.91</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>276.18</v>
+        <v>4340.8</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>225</v>
+        <v>3880.6</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="I121" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>RRKABEL</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="n">
-        <v>2111.68</v>
-      </c>
-      <c r="D122" s="7" t="n">
-        <v>1567.05</v>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>2395.2</v>
-      </c>
-      <c r="G122" s="7" t="n">
-        <v>1964.3</v>
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>RAINBOW</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="n">
+        <v>1491.49</v>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>1307.93</v>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="n">
+        <v>1525.4</v>
+      </c>
+      <c r="G122" s="8" t="n">
+        <v>1400</v>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="I122" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5167,76 +5243,76 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1184.8</v>
+        <v>367.09</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>949.3</v>
+        <v>317.36</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1234.3</v>
+        <v>372.95</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1109.2</v>
+        <v>345.7</v>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="n">
-        <v>443</v>
-      </c>
-      <c r="D124" s="7" t="n">
-        <v>328.1</v>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="G124" s="7" t="n">
-        <v>433.25</v>
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="n">
+        <v>284.91</v>
+      </c>
+      <c r="D124" s="8" t="n">
+        <v>220.16</v>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="n">
+        <v>321.65</v>
+      </c>
+      <c r="G124" s="8" t="n">
+        <v>255.7</v>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="I124" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5245,72 +5321,76 @@
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1023.75</v>
+        <v>607</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>901.3</v>
+        <v>530.1</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1042.15</v>
+        <v>651.15</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>879.1</v>
+        <v>550.05</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I125" s="3" t="inlineStr"/>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>STARHEALTH</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="n">
-        <v>535.95</v>
-      </c>
-      <c r="D126" s="7" t="n">
-        <v>491.9</v>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>588.95</v>
-      </c>
-      <c r="G126" s="7" t="n">
-        <v>513</v>
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="n">
+        <v>2549</v>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>1964.3</v>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>2602.8</v>
+      </c>
+      <c r="G126" s="8" t="n">
+        <v>2164</v>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="I126" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5319,76 +5399,76 @@
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>58.42</v>
+        <v>41.89</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>51.31</v>
+        <v>38.52</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>58.9</v>
+        <v>43.4</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>52.56</v>
+        <v>39.33</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>SYRMA</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="n">
-        <v>1188</v>
-      </c>
-      <c r="D128" s="7" t="n">
-        <v>957.4</v>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="n">
-        <v>1396.3</v>
-      </c>
-      <c r="G128" s="7" t="n">
-        <v>1085.9</v>
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D128" s="8" t="n">
+        <v>1109.2</v>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="n">
+        <v>1315.1</v>
+      </c>
+      <c r="G128" s="8" t="n">
+        <v>1191.1</v>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="I128" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5397,224 +5477,228 @@
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>TARIL</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>338</v>
+        <v>509.9</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>287.5</v>
+        <v>433.25</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>351.35</v>
+        <v>522.85</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>299.7</v>
+        <v>443.35</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="I129" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>TATACAP</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C130" s="7" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D130" s="7" t="n">
-        <v>296.8</v>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>365.9</v>
-      </c>
-      <c r="G130" s="7" t="n">
-        <v>296</v>
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="n">
+        <v>638.8</v>
+      </c>
+      <c r="D130" s="8" t="n">
+        <v>565.45</v>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="n">
+        <v>660.15</v>
+      </c>
+      <c r="G130" s="8" t="n">
+        <v>579.9</v>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr"/>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>TBOTEK</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1310.3</v>
+        <v>1846.4</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>1126.4</v>
+        <v>1700.4</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1429.7</v>
+        <v>1882</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1163.5</v>
+        <v>1758.6</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>TEJASNET</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>554.95</v>
-      </c>
-      <c r="D132" s="7" t="n">
-        <v>414.5</v>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F132" s="7" t="n">
-        <v>612.5</v>
-      </c>
-      <c r="G132" s="7" t="n">
-        <v>518.2</v>
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>SHYAMMETL</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="n">
+        <v>1012.24</v>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>931.38</v>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>1031.3</v>
+      </c>
+      <c r="G132" s="8" t="n">
+        <v>916.1</v>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I132" s="7" t="inlineStr"/>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>433.45</v>
+        <v>632.2</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>402.55</v>
+        <v>582.1</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>475.45</v>
+        <v>769.4</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>400.1</v>
+        <v>615.4</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr"/>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="n">
-        <v>5075</v>
-      </c>
-      <c r="D134" s="7" t="n">
-        <v>4056.7</v>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="n">
-        <v>5159.5</v>
-      </c>
-      <c r="G134" s="7" t="n">
-        <v>4533.3</v>
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>SONATSOFTW</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="n">
+        <v>320.53</v>
+      </c>
+      <c r="D134" s="8" t="n">
+        <v>248.02</v>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="G134" s="8" t="n">
+        <v>261.9</v>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5623,76 +5707,76 @@
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>869.7</v>
+        <v>597.4</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>721.2</v>
+        <v>513</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>880.7</v>
+        <v>601</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>790</v>
+        <v>570.1</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>TRAVELFOOD</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="n">
-        <v>1318.8</v>
-      </c>
-      <c r="D136" s="7" t="n">
-        <v>1040</v>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="n">
-        <v>1323.4</v>
-      </c>
-      <c r="G136" s="7" t="n">
-        <v>1168</v>
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>SUMICHEM</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="n">
+        <v>506.08</v>
+      </c>
+      <c r="D136" s="8" t="n">
+        <v>410.56</v>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="n">
+        <v>510.3</v>
+      </c>
+      <c r="G136" s="8" t="n">
+        <v>424.15</v>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5701,76 +5785,76 @@
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>2903.71</v>
+        <v>4635.56</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>2649.82</v>
+        <v>3979.02</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>3282.6</v>
+        <v>4665.6</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>2680</v>
+        <v>4343</v>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="n">
-        <v>171.79</v>
-      </c>
-      <c r="D138" s="7" t="n">
-        <v>156.21</v>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="n">
-        <v>172.43</v>
-      </c>
-      <c r="G138" s="7" t="n">
-        <v>160.1</v>
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="n">
+        <v>1897.43</v>
+      </c>
+      <c r="D138" s="8" t="n">
+        <v>1752.21</v>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="n">
+        <v>1990.5</v>
+      </c>
+      <c r="G138" s="8" t="n">
+        <v>1860.2</v>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5779,72 +5863,76 @@
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1342.1</v>
+        <v>270</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>1236</v>
+        <v>235.75</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1350.4</v>
+        <v>284.86</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>1229.2</v>
+        <v>238.51</v>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr"/>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="n">
-        <v>1390.18</v>
-      </c>
-      <c r="D140" s="7" t="n">
-        <v>1227.03</v>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="n">
-        <v>1521.9</v>
-      </c>
-      <c r="G140" s="7" t="n">
-        <v>1320</v>
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>TBOTEK</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="n">
+        <v>1503.9</v>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>1531.2</v>
+      </c>
+      <c r="G140" s="8" t="n">
+        <v>1400.1</v>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="I140" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5853,76 +5941,76 @@
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>145.8</v>
+        <v>1548.75</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>127.3</v>
+        <v>1309.96</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>158.84</v>
+        <v>1651.3</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>133.34</v>
+        <v>1355.6</v>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="I141" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>YESBANK</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="D142" s="7" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="G142" s="7" t="n">
-        <v>22.18</v>
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="n">
+        <v>4427.17</v>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>3949.84</v>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>4875.2</v>
+      </c>
+      <c r="G142" s="8" t="n">
+        <v>4383.1</v>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="I142" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5931,76 +6019,76 @@
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>ZEEL</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>97</v>
+        <v>435</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>81.81999999999999</v>
+        <v>357.05</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>103.51</v>
+        <v>436.8</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>91.31999999999999</v>
+        <v>398</v>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="I143" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>ZENTEC</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C144" s="7" t="n">
-        <v>1721.7</v>
-      </c>
-      <c r="D144" s="7" t="n">
-        <v>1466.1</v>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="n">
-        <v>1773.4</v>
-      </c>
-      <c r="G144" s="7" t="n">
-        <v>1582.3</v>
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="n">
+        <v>4742.9</v>
+      </c>
+      <c r="D144" s="8" t="n">
+        <v>4240.3</v>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>5122.8</v>
+      </c>
+      <c r="G144" s="8" t="n">
+        <v>4574.3</v>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="I144" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -6009,100 +6097,256 @@
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>ZFCVINDIA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>2558.17</v>
+        <v>3602.3</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>2313.33</v>
+        <v>3265.6</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>2566</v>
+        <v>4313.1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>2341.67</v>
+        <v>3463.4</v>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="I145" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>ZYDUSWELL</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C146" s="7" t="n">
-        <v>542</v>
-      </c>
-      <c r="D146" s="7" t="n">
-        <v>480</v>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F146" s="7" t="n">
-        <v>575.4</v>
-      </c>
-      <c r="G146" s="7" t="n">
-        <v>486.05</v>
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>1276</v>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>1418.8</v>
+      </c>
+      <c r="G146" s="8" t="n">
+        <v>1314.9</v>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I146" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>Total Breakout Stocks: 144</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="10" t="inlineStr">
-        <is>
-          <t>Full Breakout (Close &gt; Prev High  AND  Low &gt; Prev Low): 116</t>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>11440.48</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>10491.84</v>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>11903</v>
+      </c>
+      <c r="G147" s="4" t="n">
+        <v>11288</v>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="n">
+        <v>1385.23</v>
+      </c>
+      <c r="D148" s="8" t="n">
+        <v>1219.81</v>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="n">
+        <v>1515.9</v>
+      </c>
+      <c r="G148" s="8" t="n">
+        <v>1350.7</v>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>1153.9</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>1031.3</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>1076.2</v>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="n">
+        <v>1525</v>
+      </c>
+      <c r="D150" s="8" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>1650.6</v>
+      </c>
+      <c r="G150" s="8" t="n">
+        <v>1408.5</v>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>Total Breakout Stocks: 148</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>Full Breakout (Close &gt; Prev High  AND  Low &gt; Prev Low): 142</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A148:D148"/>
-    <mergeCell ref="A149:D149"/>
+    <mergeCell ref="A153:D153"/>
+    <mergeCell ref="A152:D152"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Monthly_Breakout_Report.xlsx
+++ b/Monthly_Breakout_Report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monthly Breakout" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Breakout" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Monthly Breakout Screener  —  Generated: 01 Aug 2026 11:45 IST</t>
+          <t>NSE Monthly Breakout Screener  —  Generated: 01 Sep 2026 15:08 IST</t>
         </is>
       </c>
     </row>
@@ -583,30 +583,30 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>33805.42</v>
+        <v>1170</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>30567.31</v>
+        <v>1060.6</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>34615</v>
+        <v>1204</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>33040</v>
+        <v>1136.6</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -622,30 +622,30 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>26553.64</v>
+        <v>516.95</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>24623.8</v>
+        <v>458.3</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>27800</v>
+        <v>540.35</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>25370</v>
+        <v>480.55</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
@@ -661,30 +661,30 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>399.35</v>
+        <v>1087.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>334.8</v>
+        <v>957.8</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>404.3</v>
+        <v>1136</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>384</v>
+        <v>1062.3</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -700,30 +700,30 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1364.92</v>
+        <v>2176.2</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1152.99</v>
+        <v>1945.1</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1418.1</v>
+        <v>2182.9</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1323.6</v>
+        <v>2028.5</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -739,30 +739,30 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1047</v>
+        <v>819</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>850.5</v>
+        <v>732</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1070.3</v>
+        <v>924.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>957.8</v>
+        <v>802.2</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -778,30 +778,30 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1614.8</v>
+        <v>15849</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1445</v>
+        <v>13282</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1645.4</v>
+        <v>17803</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>1470</v>
+        <v>14321</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -817,30 +817,30 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1189.61</v>
+        <v>1908</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>743.59</v>
+        <v>1750.1</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1280.8</v>
+        <v>2265.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1163</v>
+        <v>1820.3</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -856,30 +856,30 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>249.25</v>
+        <v>940.1</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>182.37</v>
+        <v>850.6</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>290.16</v>
+        <v>951.25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>230.41</v>
+        <v>875</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -895,30 +895,30 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1535</v>
+        <v>167.55</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1390.5</v>
+        <v>147.59</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1586</v>
+        <v>175.77</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1415.6</v>
+        <v>169.13</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -934,30 +934,30 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5608</v>
+        <v>1502.04</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>5162.5</v>
+        <v>1309.54</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>5751.5</v>
+        <v>1532.3</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>5487</v>
+        <v>1418</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -973,30 +973,30 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2032.7</v>
+        <v>1345</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1710.6</v>
+        <v>1116.2</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2073.7</v>
+        <v>1616.3</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1945.1</v>
+        <v>1242</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1012,30 +1012,30 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>597.8200000000001</v>
+        <v>1090.4</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>509.46</v>
+        <v>960</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>624.5</v>
+        <v>1091</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>513</v>
+        <v>1035.2</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -1051,30 +1051,30 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8770</v>
+        <v>1636.8</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7816</v>
+        <v>1512</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8957</v>
+        <v>1637</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>8611.5</v>
+        <v>1536.8</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1090,30 +1090,30 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>892.65</v>
+        <v>11590</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>789.12</v>
+        <v>9716</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>910.45</v>
+        <v>11910</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>829.1</v>
+        <v>11456</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -1129,30 +1129,30 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>162.2</v>
+        <v>641.95</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>138.03</v>
+        <v>541.55</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>166.18</v>
+        <v>654.85</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>147.59</v>
+        <v>592.55</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1168,69 +1168,65 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>BEML</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1147.4</v>
+        <v>1890</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>927.6</v>
+        <v>1697</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1260.3</v>
+        <v>1984.9</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1116.2</v>
+        <v>1668.1</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>10619</v>
+        <v>42703.98</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>9501</v>
+        <v>39445.43</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11520.5</v>
+        <v>48780</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>9716</v>
+        <v>41000</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1246,30 +1242,30 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1805.7</v>
+        <v>579.99</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1640.5</v>
+        <v>494.64</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2029.1</v>
+        <v>642.25</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1741.5</v>
+        <v>564.1</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -1285,30 +1281,30 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>10995</v>
+        <v>182.84</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9816</v>
+        <v>176.99</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11343</v>
+        <v>185.24</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>10132</v>
+        <v>184.9</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1324,30 +1320,30 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1010.95</v>
+        <v>874.9</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>860.45</v>
+        <v>785.05</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1141.2</v>
+        <v>901.2</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>993.4</v>
+        <v>807.95</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1363,30 +1359,30 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2282.74</v>
+        <v>1297.42</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1966.33</v>
+        <v>1034.87</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2473.5</v>
+        <v>1352.4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1982.1</v>
+        <v>1220.3</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1402,30 +1398,30 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>570</v>
+        <v>809</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>513.5</v>
+        <v>715.5</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>586.2</v>
+        <v>836.45</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>541.55</v>
+        <v>735</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -1441,30 +1437,30 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1903.74</v>
+        <v>1760.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1746.62</v>
+        <v>1359.03</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1972</v>
+        <v>2014.6</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1845.6</v>
+        <v>1719</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1480,30 +1476,30 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>1510.58</v>
+        <v>1429.4</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>1414.44</v>
+        <v>1238</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>1607.5</v>
+        <v>1481.9</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>1437.1</v>
+        <v>1356.4</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1519,30 +1515,30 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BLUEDART</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5079.5</v>
+        <v>10275</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4628.5</v>
+        <v>8955.5</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5160.3</v>
+        <v>10898</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4716.1</v>
+        <v>9922.5</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -1558,30 +1554,30 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>547.6</v>
+        <v>4540</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>434.8</v>
+        <v>3855</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>626.25</v>
+        <v>4703.2</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>513.1</v>
+        <v>4309.9</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -1597,30 +1593,30 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5211.7</v>
+        <v>904.95</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4952.52</v>
+        <v>814.45</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5416.5</v>
+        <v>1107.45</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5115</v>
+        <v>839</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -1636,30 +1632,30 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>CANHLIFE</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>132.6</v>
+        <v>107</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>146.45</v>
+        <v>146.11</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>138.11</v>
+        <v>112.55</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -1675,30 +1671,30 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1315.4</v>
+        <v>8090</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1003.1</v>
+        <v>6530.5</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1367.8</v>
+        <v>9239</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1274.6</v>
+        <v>8105</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -1714,30 +1710,30 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>231.36</v>
+        <v>7930</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>195.09</v>
+        <v>7053.5</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>232.38</v>
+        <v>8059</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>218.59</v>
+        <v>7852</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -1753,30 +1749,30 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1249</v>
+        <v>788.75</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1060.2</v>
+        <v>709.25</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1260.6</v>
+        <v>795.3</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1080</v>
+        <v>759</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -1792,30 +1788,30 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>760</v>
+        <v>2835</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>632.05</v>
+        <v>2548.6</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>822.95</v>
+        <v>2944.8</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>751.7</v>
+        <v>2731.4</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -1831,30 +1827,30 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1823.18</v>
+        <v>246.66</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1444.03</v>
+        <v>219.44</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1849.9</v>
+        <v>253.72</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1660.4</v>
+        <v>222.38</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -1870,30 +1866,30 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>1550.44</v>
+        <v>316.35</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1353.09</v>
+        <v>265.3</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1721</v>
+        <v>328</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>1362.2</v>
+        <v>300.05</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
@@ -1909,30 +1905,30 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>484.65</v>
+        <v>1185.8</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>437.45</v>
+        <v>956.2</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>525.5</v>
+        <v>1291.15</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>448.45</v>
+        <v>988</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -1948,30 +1944,30 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>1399.52</v>
+        <v>4653.2</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>1016.12</v>
+        <v>3814.2</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1420.8</v>
+        <v>4672.1</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>1238</v>
+        <v>4376.8</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -1987,30 +1983,30 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1496</v>
+        <v>2566.61</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1229.1</v>
+        <v>2333.47</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1592.8</v>
+        <v>2873.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1456.5</v>
+        <v>2494.1</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
@@ -2026,30 +2022,30 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>4240.22</v>
+        <v>2679</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>3766.32</v>
+        <v>2370</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>4359.8</v>
+        <v>3106.4</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>3855</v>
+        <v>2515</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -2065,30 +2061,30 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1773.3</v>
+        <v>2323.79</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1605</v>
+        <v>2140.67</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1799.7</v>
+        <v>2515</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1683</v>
+        <v>2162</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -2104,30 +2100,30 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>6859.21</v>
+        <v>687.5</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>6424.01</v>
+        <v>570</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>8056</v>
+        <v>696</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>6530.5</v>
+        <v>654.35</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2143,30 +2139,30 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>12930</v>
+        <v>3235.92</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>11153</v>
+        <v>3050.5</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>14049</v>
+        <v>3258</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>11785</v>
+        <v>3103.1</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
@@ -2182,30 +2178,30 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>636.01</v>
+        <v>4659.56</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>548.61</v>
+        <v>4297.09</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>659.3</v>
+        <v>4861.1</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>618</v>
+        <v>4603.3</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
@@ -2221,30 +2217,30 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1551</v>
+        <v>683</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1320</v>
+        <v>509.1</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1845.5</v>
+        <v>737.35</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1328.2</v>
+        <v>652.4</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -2260,30 +2256,30 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>7673.64</v>
+        <v>5394.7</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>6870.55</v>
+        <v>4774</v>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>7833.5</v>
+        <v>5600</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>7053.5</v>
+        <v>5388</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
@@ -2299,30 +2295,30 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1944</v>
+        <v>229.5</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1667</v>
+        <v>181.05</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1960.1</v>
+        <v>251.47</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1751</v>
+        <v>195.7</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -2338,30 +2334,30 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>2988.19</v>
+        <v>998</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2669.79</v>
+        <v>935.1</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>3086</v>
+        <v>1037.4</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>2880</v>
+        <v>981.35</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
@@ -2377,30 +2373,30 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>267.5</v>
+        <v>512</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>234.25</v>
+        <v>469</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>302.45</v>
+        <v>533.55</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>265.3</v>
+        <v>490.05</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -2416,30 +2412,30 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>408.54</v>
+        <v>545</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>375.9</v>
+        <v>514.95</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>449.8</v>
+        <v>622</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>385.8</v>
+        <v>541.45</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -2455,30 +2451,30 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>331.8</v>
+        <v>2187.11</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>284.85</v>
+        <v>1877.47</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>358.85</v>
+        <v>2267</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>323</v>
+        <v>2160.1</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -2494,30 +2490,30 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>525.9400000000001</v>
+        <v>89.94</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>413.85</v>
+        <v>80.17</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>547.95</v>
+        <v>92.66</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>508</v>
+        <v>80.5</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
@@ -2533,30 +2529,30 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>3990</v>
+        <v>79.64</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>3451.2</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4366.8</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>3814.2</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
@@ -2572,30 +2568,30 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>274.8</v>
+        <v>623</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>227.2</v>
+        <v>494.65</v>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>302.12</v>
+        <v>635.65</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>228.7</v>
+        <v>602.4</v>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
@@ -2611,30 +2607,30 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1285</v>
+        <v>538.5</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>975.6</v>
+        <v>481.95</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1441.8</v>
+        <v>567.35</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1215</v>
+        <v>512.3</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
@@ -2650,30 +2646,30 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>178.47</v>
+        <v>874.9</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>161.18</v>
+        <v>769.25</v>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>181.44</v>
+        <v>882.4</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>167.27</v>
+        <v>837.3</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
@@ -2689,46 +2685,42 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>2460.9</v>
+        <v>1938.17</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>2088.1</v>
+        <v>1675.88</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2655.4</v>
+        <v>1959.8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2370</v>
+        <v>1674.4</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I57" s="3" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -2737,10 +2729,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1056.8</v>
+        <v>2317.5</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>975.4</v>
+        <v>2080.9</v>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
@@ -2748,10 +2740,10 @@
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>1070.4</v>
+        <v>2408.9</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>1013.9</v>
+        <v>2267.1</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
@@ -2767,30 +2759,30 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>GODREJIND</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1178.5</v>
+        <v>278.95</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1005</v>
+        <v>246.5</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1317.6</v>
+        <v>308.6</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>1164.4</v>
+        <v>253.25</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -2806,30 +2798,30 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>1878.52</v>
+        <v>1118</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1602.35</v>
+        <v>1008.29</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>2105.7</v>
+        <v>1179.2</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>1873.8</v>
+        <v>1086</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
@@ -2845,30 +2837,30 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>816</v>
+        <v>1304.5</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>734.97</v>
+        <v>1210.7</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>824.65</v>
+        <v>1337.5</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>804.5</v>
+        <v>1250.4</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
@@ -2884,30 +2876,30 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>4535</v>
+        <v>457.4</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>4148.8</v>
+        <v>408.55</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>4646.5</v>
+        <v>504</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>4305.8</v>
+        <v>439.95</v>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
@@ -2923,104 +2915,104 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1209.1</v>
+        <v>839</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1123.6</v>
+        <v>745.75</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1260.7</v>
+        <v>1029.8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1141.2</v>
+        <v>738.9</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I63" s="3" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>1244.3</v>
+        <v>3859.8</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1057.8</v>
+        <v>3131</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>1346.9</v>
+        <v>3943.1</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>1030</v>
+        <v>3535</v>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>567.89</v>
+        <v>5485.5</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>502.16</v>
+        <v>4745.5</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>657.25</v>
+        <v>5570</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>509.1</v>
+        <v>4963.2</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
@@ -3036,30 +3028,30 @@
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>4999.86</v>
+        <v>405</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>4603.78</v>
+        <v>368.4</v>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>5386</v>
+        <v>423.7</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>4774</v>
+        <v>386.5</v>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
@@ -3075,30 +3067,30 @@
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>552.5</v>
+        <v>1919.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>472</v>
+        <v>1610.1</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>561.65</v>
+        <v>1936.4</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>512.5</v>
+        <v>1863</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
@@ -3114,30 +3106,30 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
-        <v>718</v>
+        <v>1826.6</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>580.9</v>
+        <v>1448.2</v>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>750.65</v>
+        <v>1938.5</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>635.85</v>
+        <v>1769.4</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
@@ -3153,30 +3145,30 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>2059</v>
+        <v>575.7</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1847.1</v>
+        <v>516.95</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2180.7</v>
+        <v>636.15</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1895.4</v>
+        <v>559.3</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
@@ -3192,30 +3184,30 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>1404</v>
+        <v>1593</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1213.7</v>
+        <v>1484.8</v>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>1435.4</v>
+        <v>1700.4</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>1367.7</v>
+        <v>1499</v>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
@@ -3231,30 +3223,30 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>81.45999999999999</v>
+        <v>415.8</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>69.53</v>
+        <v>366.12</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>84.68000000000001</v>
+        <v>437.85</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>77.47</v>
+        <v>408.7</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -3270,30 +3262,30 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>129.22</v>
+        <v>3030.57</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>116.8</v>
+        <v>2571.2</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>132.24</v>
+        <v>3332</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>116.26</v>
+        <v>2565.5</v>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
@@ -3305,30 +3297,30 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>546.15</v>
+        <v>1437.49</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>459.7</v>
+        <v>1295.44</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>608.65</v>
+        <v>1472.2</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>494.65</v>
+        <v>1380</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
@@ -3344,30 +3336,30 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>1758</v>
+        <v>195.92</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>1619.2</v>
+        <v>173.5</v>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>1848.9</v>
+        <v>208.63</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>1670.1</v>
+        <v>180.26</v>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
@@ -3383,30 +3375,30 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>953.5</v>
+        <v>152.4</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>881</v>
+        <v>136.71</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1012.45</v>
+        <v>165.6</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>927.05</v>
+        <v>148.34</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
@@ -3422,30 +3414,30 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>1736</v>
+        <v>989.75</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1470</v>
+        <v>835.1</v>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>1747.8</v>
+        <v>1038.3</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>1681.7</v>
+        <v>852.7</v>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
@@ -3461,30 +3453,30 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>2317.5</v>
+        <v>367.57</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>2080.9</v>
+        <v>330.66</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2416.1</v>
+        <v>389.3</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>2267.1</v>
+        <v>353.5</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
@@ -3500,30 +3492,30 @@
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>246.85</v>
+        <v>1268.9</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>227</v>
+        <v>974.6</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>256.46</v>
+        <v>1354</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>229</v>
+        <v>1222.6</v>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
@@ -3539,30 +3531,30 @@
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>732.4</v>
+        <v>7936</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>652.25</v>
+        <v>7289</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>734.8</v>
+        <v>8567.5</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>677.6</v>
+        <v>7510</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
@@ -3578,65 +3570,69 @@
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>437.46</v>
+        <v>4620.22</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>409.93</v>
+        <v>4112.44</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>438.25</v>
+        <v>5272.2</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>408.55</v>
+        <v>4540</v>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>657.6900000000001</v>
+        <v>20089</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>597.99</v>
+        <v>18055</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>735.7</v>
+        <v>23205</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>610.7</v>
+        <v>19005</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -3652,69 +3648,65 @@
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>NSLNISP</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>791.1</v>
+        <v>45.14</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>580.1</v>
+        <v>40.66</v>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>808.65</v>
+        <v>49.02</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>745.75</v>
+        <v>39.3</v>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I82" s="7" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>391.5</v>
+        <v>11979</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>327.05</v>
+        <v>9937</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>612.6</v>
+        <v>12190</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>348.35</v>
+        <v>11160</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
@@ -3730,30 +3722,30 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>299.32</v>
+        <v>465</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>266.87</v>
+        <v>412.05</v>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
-        <v>342.45</v>
+        <v>469.85</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>288.8</v>
+        <v>435.45</v>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
@@ -3769,30 +3761,30 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>3399</v>
+        <v>159.5</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>3018.1</v>
+        <v>132.9</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>3804.6</v>
+        <v>165.88</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>3131</v>
+        <v>143.7</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
@@ -3808,30 +3800,30 @@
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>915.6</v>
+        <v>1407</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>789.36</v>
+        <v>1150.5</v>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
-        <v>937.9</v>
+        <v>1650.9</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>838</v>
+        <v>1344.4</v>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
@@ -3847,30 +3839,30 @@
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1798.21</v>
+        <v>5698</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>1496.12</v>
+        <v>4311.7</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1905.2</v>
+        <v>5875</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1610.1</v>
+        <v>5319.5</v>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
@@ -3886,30 +3878,30 @@
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>1531.2</v>
+        <v>284.25</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1342.9</v>
+        <v>267.35</v>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
-        <v>1816.2</v>
+        <v>290.95</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>1448.2</v>
+        <v>273</v>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
@@ -3925,30 +3917,30 @@
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>532.5</v>
+        <v>1637.9</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>482.15</v>
+        <v>1537.1</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>561.4</v>
+        <v>1656</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>516.95</v>
+        <v>1602</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
@@ -3964,30 +3956,30 @@
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>1846.8</v>
+        <v>163.99</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1670</v>
+        <v>138.29</v>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2047</v>
+        <v>169.67</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>1708.9</v>
+        <v>139.61</v>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
@@ -4003,30 +3995,30 @@
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>972</v>
+        <v>2220</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>848</v>
+        <v>1970.5</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1243.95</v>
+        <v>2278.4</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>954.3</v>
+        <v>2007</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
@@ -4042,30 +4034,30 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>397.8</v>
+        <v>113.38</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>364.05</v>
+        <v>100.45</v>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
-        <v>410.35</v>
+        <v>115.4</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>367</v>
+        <v>112.3</v>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
@@ -4081,30 +4073,30 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>4360</v>
+        <v>1132.7</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>3528</v>
+        <v>1024.2</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>4362.1</v>
+        <v>1178</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>3535.2</v>
+        <v>1049.7</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
@@ -4120,65 +4112,69 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>3549</v>
+        <v>1705</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>3090</v>
+        <v>1502.1</v>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
-        <v>3555.4</v>
+        <v>1811.5</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>3030</v>
+        <v>1578.4</v>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>3175.16</v>
+        <v>202.26</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>2870.26</v>
+        <v>166.11</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>3398.5</v>
+        <v>218.68</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3079.4</v>
+        <v>193.03</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
@@ -4194,30 +4190,30 @@
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>325.09</v>
+        <v>18599</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>268.31</v>
+        <v>16922</v>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
-        <v>385.75</v>
+        <v>22110</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>312</v>
+        <v>17776</v>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
@@ -4233,30 +4229,30 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>330.9</v>
+        <v>1163</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>282.55</v>
+        <v>962</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>371.85</v>
+        <v>1220.9</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>315</v>
+        <v>1130</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
@@ -4272,30 +4268,30 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>MAPMYINDIA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>934.85</v>
+        <v>4494.4</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>805</v>
+        <v>3880.6</v>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
-        <v>1181.65</v>
+        <v>4606</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>813.5</v>
+        <v>4349.9</v>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
@@ -4311,30 +4307,30 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>840.8099999999999</v>
+        <v>338.5</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>791.23</v>
+        <v>255.7</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>870.65</v>
+        <v>366</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>829.9</v>
+        <v>319.5</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
@@ -4350,30 +4346,30 @@
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>14201</v>
+        <v>654.65</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>12700</v>
+        <v>550.05</v>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>14234</v>
+        <v>751.25</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>13197</v>
+        <v>642.35</v>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
@@ -4389,30 +4385,30 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1335.9</v>
+        <v>2775</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1153</v>
+        <v>2164</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1405.6</v>
+        <v>2830.1</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1295.9</v>
+        <v>2598.7</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
@@ -4428,30 +4424,30 @@
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>132653.46</v>
+        <v>46.13</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>121837.34</v>
+        <v>39.24</v>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
-        <v>132770</v>
+        <v>46.34</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>127480</v>
+        <v>41.77</v>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
@@ -4467,30 +4463,30 @@
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1025.83</v>
+        <v>175.9</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>946.13</v>
+        <v>158.01</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1226.25</v>
+        <v>200</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>974.6</v>
+        <v>158.73</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
@@ -4506,30 +4502,30 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>1447.94</v>
+        <v>1338</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1361.55</v>
+        <v>1191.1</v>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F104" s="8" t="n">
-        <v>1509.6</v>
+        <v>1485</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>1405.1</v>
+        <v>1315.2</v>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
@@ -4545,30 +4541,30 @@
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>18740.36</v>
+        <v>205.06</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>16370.74</v>
+        <v>171.9</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>19043</v>
+        <v>239.74</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>18055</v>
+        <v>182.06</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
@@ -4584,30 +4580,30 @@
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>532.04</v>
+        <v>95</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>430.18</v>
+        <v>88.56</v>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>555.7</v>
+        <v>98.61</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>461.25</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
@@ -4623,30 +4619,30 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1997.87</v>
+        <v>1087.1</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>1829.54</v>
+        <v>913.66</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2029.2</v>
+        <v>1099.8</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>1952</v>
+        <v>970</v>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
@@ -4662,30 +4658,30 @@
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>312.9</v>
+        <v>3855</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>257.8</v>
+        <v>3398.1</v>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>333.4</v>
+        <v>4089</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>305.6</v>
+        <v>3694.2</v>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
@@ -4701,30 +4697,30 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1782.97</v>
+        <v>19187</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>1573.4</v>
+        <v>17028</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1827.7</v>
+        <v>20400</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>1758.5</v>
+        <v>17816</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
@@ -4740,30 +4736,30 @@
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>11055</v>
+        <v>773.2</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>9050</v>
+        <v>615.4</v>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>11186</v>
+        <v>815</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>9937</v>
+        <v>768.05</v>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
@@ -4779,30 +4775,30 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>140.4</v>
+        <v>3538.1</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>120.49</v>
+        <v>3140</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>147.33</v>
+        <v>3636.9</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>132.9</v>
+        <v>3383</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
@@ -4818,30 +4814,30 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>1159.2</v>
+        <v>1466.5</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>1014</v>
+        <v>1255.72</v>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
-        <v>1343</v>
+        <v>1474.3</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>1150.5</v>
+        <v>1351.6</v>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
@@ -4857,30 +4853,30 @@
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>4632.94</v>
+        <v>777</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>4290.49</v>
+        <v>661.5</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>4823.9</v>
+        <v>834.35</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>4426</v>
+        <v>748</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
@@ -4896,30 +4892,30 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>579</v>
+        <v>1569</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>457</v>
+        <v>1400.1</v>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>613.35</v>
+        <v>1696.6</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>533.6</v>
+        <v>1540.4</v>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
@@ -4935,30 +4931,30 @@
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1609.11</v>
+        <v>509.4</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>1419.78</v>
+        <v>461.05</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1611.4</v>
+        <v>553.8</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>1537.1</v>
+        <v>491.4</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
@@ -4974,65 +4970,69 @@
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
-        <v>110.5</v>
+        <v>4886</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>102.67</v>
+        <v>4383.1</v>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
-        <v>112.71</v>
+        <v>5169.2</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>100.45</v>
+        <v>4851.8</v>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr"/>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>442.65</v>
+        <v>446.8</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>370.05</v>
+        <v>398</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>463.55</v>
+        <v>466.3</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>434.4</v>
+        <v>434.55</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
@@ -5048,30 +5048,30 @@
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C118" s="8" t="n">
-        <v>175.95</v>
+        <v>179.4</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>158.1</v>
+        <v>153.5</v>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F118" s="8" t="n">
-        <v>195.61</v>
+        <v>186</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>166.11</v>
+        <v>171.4</v>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
@@ -5087,30 +5087,30 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1580.6</v>
+        <v>1188</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>1311</v>
+        <v>1076.2</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1616.2</v>
+        <v>1280</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>1564.8</v>
+        <v>1185</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
@@ -5126,30 +5126,30 @@
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>URBANCO</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>1003.45</v>
+        <v>140.23</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>934.2</v>
+        <v>126.8</v>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
-        <v>1130.6</v>
+        <v>168.41</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>962</v>
+        <v>136.3</v>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
@@ -5165,30 +5165,30 @@
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>3966.4</v>
+        <v>282.85</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>3418.91</v>
+        <v>249.7</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>4340.8</v>
+        <v>287.95</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>3880.6</v>
+        <v>261.35</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
@@ -5204,30 +5204,30 @@
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>VIJAYA</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>1491.49</v>
+        <v>1440</v>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1307.93</v>
+        <v>1291</v>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
-        <v>1525.4</v>
+        <v>1472.4</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>1400</v>
+        <v>1334.6</v>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
@@ -5243,30 +5243,30 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>367.09</v>
+        <v>1700</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>317.36</v>
+        <v>1408.5</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>372.95</v>
+        <v>2373.8</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>345.7</v>
+        <v>1659.2</v>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
@@ -5282,69 +5282,65 @@
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
-        <v>284.91</v>
+        <v>174.97</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>220.16</v>
+        <v>155.21</v>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
-        <v>321.65</v>
+        <v>190.46</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>255.7</v>
+        <v>152.98</v>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I124" s="7" t="inlineStr"/>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>607</v>
+        <v>820.1</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>530.1</v>
+        <v>748.67</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>651.15</v>
+        <v>841.15</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>550.05</v>
+        <v>751</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
@@ -5360,993 +5356,57 @@
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>2549</v>
+        <v>1181.5</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>1964.3</v>
+        <v>1095.1</v>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F126" s="8" t="n">
-        <v>2602.8</v>
+        <v>1189.2</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>2164</v>
+        <v>1092.6</v>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>SAGILITY</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>41.89</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="G127" s="4" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>SAILIFE</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D128" s="8" t="n">
-        <v>1109.2</v>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="n">
-        <v>1315.1</v>
-      </c>
-      <c r="G128" s="8" t="n">
-        <v>1191.1</v>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>509.9</v>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>433.25</v>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="n">
-        <v>522.85</v>
-      </c>
-      <c r="G129" s="4" t="n">
-        <v>443.35</v>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="n">
-        <v>638.8</v>
-      </c>
-      <c r="D130" s="8" t="n">
-        <v>565.45</v>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F130" s="8" t="n">
-        <v>660.15</v>
-      </c>
-      <c r="G130" s="8" t="n">
-        <v>579.9</v>
-      </c>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>1846.4</v>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>1700.4</v>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>1882</v>
-      </c>
-      <c r="G131" s="4" t="n">
-        <v>1758.6</v>
-      </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>SHYAMMETL</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="n">
-        <v>1012.24</v>
-      </c>
-      <c r="D132" s="8" t="n">
-        <v>931.38</v>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="n">
-        <v>1031.3</v>
-      </c>
-      <c r="G132" s="8" t="n">
-        <v>916.1</v>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I132" s="7" t="inlineStr"/>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="n">
-        <v>632.2</v>
-      </c>
-      <c r="D133" s="4" t="n">
-        <v>582.1</v>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="n">
-        <v>769.4</v>
-      </c>
-      <c r="G133" s="4" t="n">
-        <v>615.4</v>
-      </c>
-      <c r="H133" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>SONATSOFTW</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="n">
-        <v>320.53</v>
-      </c>
-      <c r="D134" s="8" t="n">
-        <v>248.02</v>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F134" s="8" t="n">
-        <v>322.45</v>
-      </c>
-      <c r="G134" s="8" t="n">
-        <v>261.9</v>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>STARHEALTH</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>597.4</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>513</v>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="n">
-        <v>601</v>
-      </c>
-      <c r="G135" s="4" t="n">
-        <v>570.1</v>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>SUMICHEM</t>
-        </is>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="n">
-        <v>506.08</v>
-      </c>
-      <c r="D136" s="8" t="n">
-        <v>410.56</v>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F136" s="8" t="n">
-        <v>510.3</v>
-      </c>
-      <c r="G136" s="8" t="n">
-        <v>424.15</v>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>SUNDARMFIN</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>4635.56</v>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>3979.02</v>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="n">
-        <v>4665.6</v>
-      </c>
-      <c r="G137" s="4" t="n">
-        <v>4343</v>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="n">
-        <v>1897.43</v>
-      </c>
-      <c r="D138" s="8" t="n">
-        <v>1752.21</v>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F138" s="8" t="n">
-        <v>1990.5</v>
-      </c>
-      <c r="G138" s="8" t="n">
-        <v>1860.2</v>
-      </c>
-      <c r="H138" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>SWIGGY</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="D139" s="4" t="n">
-        <v>235.75</v>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="n">
-        <v>284.86</v>
-      </c>
-      <c r="G139" s="4" t="n">
-        <v>238.51</v>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>TBOTEK</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="n">
-        <v>1503.9</v>
-      </c>
-      <c r="D140" s="8" t="n">
-        <v>1163.5</v>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F140" s="8" t="n">
-        <v>1531.2</v>
-      </c>
-      <c r="G140" s="8" t="n">
-        <v>1400.1</v>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="n">
-        <v>1548.75</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>1309.96</v>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="n">
-        <v>1651.3</v>
-      </c>
-      <c r="G141" s="4" t="n">
-        <v>1355.6</v>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="n">
-        <v>4427.17</v>
-      </c>
-      <c r="D142" s="8" t="n">
-        <v>3949.84</v>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F142" s="8" t="n">
-        <v>4875.2</v>
-      </c>
-      <c r="G142" s="8" t="n">
-        <v>4383.1</v>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>TMCV</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="n">
-        <v>435</v>
-      </c>
-      <c r="D143" s="4" t="n">
-        <v>357.05</v>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="n">
-        <v>436.8</v>
-      </c>
-      <c r="G143" s="4" t="n">
-        <v>398</v>
-      </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="n">
-        <v>4742.9</v>
-      </c>
-      <c r="D144" s="8" t="n">
-        <v>4240.3</v>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F144" s="8" t="n">
-        <v>5122.8</v>
-      </c>
-      <c r="G144" s="8" t="n">
-        <v>4574.3</v>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="n">
-        <v>3602.3</v>
-      </c>
-      <c r="D145" s="4" t="n">
-        <v>3265.6</v>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="n">
-        <v>4313.1</v>
-      </c>
-      <c r="G145" s="4" t="n">
-        <v>3463.4</v>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>UBL</t>
-        </is>
-      </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="n">
-        <v>1373</v>
-      </c>
-      <c r="D146" s="8" t="n">
-        <v>1276</v>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F146" s="8" t="n">
-        <v>1418.8</v>
-      </c>
-      <c r="G146" s="8" t="n">
-        <v>1314.9</v>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>11440.48</v>
-      </c>
-      <c r="D147" s="4" t="n">
-        <v>10491.84</v>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="n">
-        <v>11903</v>
-      </c>
-      <c r="G147" s="4" t="n">
-        <v>11288</v>
-      </c>
-      <c r="H147" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="n">
-        <v>1385.23</v>
-      </c>
-      <c r="D148" s="8" t="n">
-        <v>1219.81</v>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F148" s="8" t="n">
-        <v>1515.9</v>
-      </c>
-      <c r="G148" s="8" t="n">
-        <v>1350.7</v>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="n">
-        <v>1153.9</v>
-      </c>
-      <c r="D149" s="4" t="n">
-        <v>1031.3</v>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="n">
-        <v>1180.5</v>
-      </c>
-      <c r="G149" s="4" t="n">
-        <v>1076.2</v>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="n">
-        <v>1525</v>
-      </c>
-      <c r="D150" s="8" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F150" s="8" t="n">
-        <v>1650.6</v>
-      </c>
-      <c r="G150" s="8" t="n">
-        <v>1408.5</v>
-      </c>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>Total Breakout Stocks: 148</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>Full Breakout (Close &gt; Prev High  AND  Low &gt; Prev Low): 142</t>
+      <c r="I126" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>Total Breakout Stocks: 124</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>Full Breakout (Close &gt; Prev High  AND  Low &gt; Prev Low): 117</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A153:D153"/>
-    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A129:D129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
